--- a/data/hex_xlsx/ORIOLA.HE.xlsx
+++ b/data/hex_xlsx/ORIOLA.HE.xlsx
@@ -13023,12 +13023,27 @@
       <c r="P47" s="19">
         <v>572.52</v>
       </c>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="15"/>
+      <c r="Q47" s="20">
+        <f t="shared" ref="Q47:T47" si="1">SUM(Q48,Q51,Q54,Q58,Q62)</f>
+        <v>525.68</v>
+      </c>
+      <c r="R47" s="20">
+        <f t="shared" si="1"/>
+        <v>439.58</v>
+      </c>
+      <c r="S47" s="20">
+        <f t="shared" si="1"/>
+        <v>524.23</v>
+      </c>
+      <c r="T47" s="20">
+        <f t="shared" si="1"/>
+        <v>446.39</v>
+      </c>
       <c r="U47" s="15"/>
-      <c r="V47" s="15"/>
+      <c r="V47" s="20">
+        <f>SUM(V48,V51,V54,V58,V62)</f>
+        <v>559.71</v>
+      </c>
       <c r="W47" s="15"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
@@ -17026,12 +17041,24 @@
       <c r="J126" s="20">
         <v>6.89</v>
       </c>
-      <c r="K126" s="15"/>
-      <c r="L126" s="15"/>
-      <c r="M126" s="15"/>
-      <c r="N126" s="15"/>
-      <c r="O126" s="15"/>
-      <c r="P126" s="15"/>
+      <c r="K126" s="19">
+        <v>128.03</v>
+      </c>
+      <c r="L126" s="19">
+        <v>112.32</v>
+      </c>
+      <c r="M126" s="20">
+        <v>50.62</v>
+      </c>
+      <c r="N126" s="20">
+        <v>0.83</v>
+      </c>
+      <c r="O126" s="20">
+        <v>2.2</v>
+      </c>
+      <c r="P126" s="20">
+        <v>10.83</v>
+      </c>
       <c r="Q126" s="15"/>
       <c r="R126" s="15"/>
       <c r="S126" s="15"/>

--- a/data/hex_xlsx/ORIOLA.HE.xlsx
+++ b/data/hex_xlsx/ORIOLA.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="530">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1042,6 +1042,9 @@
   </si>
   <si>
     <t>Pension Loans</t>
+  </si>
+  <si>
+    <t>Loans from financial institutions LT</t>
   </si>
   <si>
     <t>Lease liabilities</t>
@@ -1731,7 +1734,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1809,6 +1812,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -17440,8 +17446,8 @@
       </c>
     </row>
     <row r="135" ht="15.0" customHeight="1">
-      <c r="A135" s="14" t="s">
-        <v>329</v>
+      <c r="A135" s="26" t="s">
+        <v>341</v>
       </c>
       <c r="B135" s="19">
         <v>354.42</v>
@@ -17492,7 +17498,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B136" s="20">
         <v>98.06</v>
@@ -17561,7 +17567,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -17596,7 +17602,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -17625,7 +17631,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B139" s="20">
         <v>20.08</v>
@@ -17694,7 +17700,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B140" s="19">
         <v>168.94</v>
@@ -17763,7 +17769,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B141" s="20">
         <v>10.63</v>
@@ -17824,7 +17830,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B142" s="20">
         <v>4.73</v>
@@ -17861,7 +17867,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B143" s="20">
         <v>5.91</v>
@@ -17902,7 +17908,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -17970,7 +17976,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B146" s="15"/>
       <c r="C146" s="21">
@@ -18009,7 +18015,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B147" s="18">
         <v>652.13</v>
@@ -18078,7 +18084,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B148" s="18">
         <v>9986.38</v>
@@ -18147,7 +18153,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B149" s="19">
         <v>427.67</v>
@@ -18212,7 +18218,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B150" s="20">
         <v>67.34</v>
@@ -18269,7 +18275,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B151" s="19">
         <v>229.19</v>
@@ -18332,7 +18338,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -18363,7 +18369,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -18398,7 +18404,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B154" s="19">
         <v>883.69</v>
@@ -18449,7 +18455,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B155" s="20">
         <v>1.18</v>
@@ -18506,7 +18512,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B156" s="22">
         <v>-173.67</v>
@@ -18557,7 +18563,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B157" s="22">
         <v>-243.37</v>
@@ -18618,7 +18624,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -18649,7 +18655,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -18680,7 +18686,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B160" s="21">
         <v>-1.18</v>
@@ -18725,7 +18731,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B161" s="18">
         <v>1190.85</v>
@@ -18833,7 +18839,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B163" s="18">
         <v>1190.85</v>
@@ -18902,7 +18908,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B164" s="15"/>
       <c r="C164" s="21">
@@ -18947,7 +18953,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B165" s="17">
         <v>11177.23</v>
@@ -19016,7 +19022,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B166" s="19">
         <v>185.25</v>
@@ -19085,7 +19091,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B167" s="19">
         <v>185.33</v>
@@ -19154,7 +19160,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B168" s="20">
         <v>0.08</v>
@@ -19223,7 +19229,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -19252,7 +19258,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -19281,7 +19287,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -19318,7 +19324,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -19349,7 +19355,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -19382,7 +19388,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -19415,7 +19421,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -19460,7 +19466,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -19505,7 +19511,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -19538,7 +19544,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -19567,7 +19573,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
@@ -19608,7 +19614,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B180" s="19">
         <v>139.41</v>
@@ -19651,7 +19657,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B181" s="20">
         <v>41.35</v>
@@ -19702,7 +19708,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B182" s="20">
         <v>36.62</v>
@@ -19739,7 +19745,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B183" s="20">
         <v>29.54</v>
@@ -19776,7 +19782,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B184" s="20">
         <v>31.9</v>
@@ -19813,7 +19819,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B185" s="15">
         <v>0.0</v>
@@ -19850,7 +19856,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B186" s="15">
         <v>0.0</v>
@@ -19887,7 +19893,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B187" s="19">
         <v>354.42</v>
@@ -19924,7 +19930,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B188" s="15"/>
       <c r="C188" s="19">
@@ -19959,7 +19965,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
@@ -19988,7 +19994,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B190" s="20">
         <v>1.0</v>
@@ -20057,7 +20063,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B191" s="19">
         <v>185.33</v>
@@ -20126,7 +20132,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B192" s="19">
         <v>185.25</v>
@@ -20195,7 +20201,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B193" s="20">
         <v>0.08</v>
@@ -20264,7 +20270,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B194" s="15"/>
       <c r="C194" s="20">
@@ -20331,7 +20337,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B195" s="15"/>
       <c r="C195" s="20">
@@ -20398,7 +20404,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B196" s="15"/>
       <c r="C196" s="20">
@@ -20465,7 +20471,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B197" s="15"/>
       <c r="C197" s="20">
@@ -20516,7 +20522,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B198" s="19">
         <v>801.0</v>
@@ -20583,7 +20589,7 @@
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
@@ -20634,7 +20640,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
@@ -20685,7 +20691,7 @@
     </row>
     <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -20724,7 +20730,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
@@ -20777,7 +20783,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B203" s="15">
         <v>34112.0</v>
@@ -21653,7 +21659,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22026,67 +22032,67 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -22159,7 +22165,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -22317,7 +22323,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B21" s="19">
         <v>140.43</v>
@@ -22381,7 +22387,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B22" s="20">
         <v>66.7</v>
@@ -22549,7 +22555,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -22579,7 +22585,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B27" s="20">
         <v>40.96</v>
@@ -22643,7 +22649,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B28" s="20">
         <v>10.53</v>
@@ -22705,7 +22711,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B29" s="19">
         <v>475.12</v>
@@ -22767,7 +22773,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B30" s="22">
         <v>-495.02</v>
@@ -22829,7 +22835,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B31" s="21">
         <v>-71.39</v>
@@ -22891,7 +22897,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B32" s="19">
         <v>1041.53</v>
@@ -22953,7 +22959,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -22987,7 +22993,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B34" s="20">
         <v>40.96</v>
@@ -23017,7 +23023,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B35" s="21">
         <v>-43.3</v>
@@ -23047,7 +23053,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -23105,7 +23111,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -23133,7 +23139,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B38" s="21">
         <v>-18.72</v>
@@ -23163,7 +23169,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -23219,7 +23225,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B40" s="21">
         <v>-40.96</v>
@@ -23281,7 +23287,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -23319,7 +23325,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -23349,7 +23355,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -23377,7 +23383,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -23413,7 +23419,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -23447,7 +23453,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -23481,7 +23487,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -23511,7 +23517,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -23541,7 +23547,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B49" s="20">
         <v>1.17</v>
@@ -23595,7 +23601,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="16" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B50" s="18">
         <v>702.15</v>
@@ -23663,7 +23669,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B51" s="21">
         <v>-38.62</v>
@@ -23719,7 +23725,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B52" s="15">
         <v>0.0</v>
@@ -23767,7 +23773,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B53" s="21">
         <v>-5.85</v>
@@ -23833,7 +23839,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -23883,7 +23889,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -23919,7 +23925,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -23959,7 +23965,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B58" s="20">
         <v>1.17</v>
@@ -23987,7 +23993,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -24015,7 +24021,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -24061,7 +24067,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -24095,7 +24101,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -24127,7 +24133,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -24155,7 +24161,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -24187,7 +24193,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -24219,7 +24225,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -24249,7 +24255,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -24279,7 +24285,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -24315,7 +24321,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B69" s="20">
         <v>47.98</v>
@@ -24345,7 +24351,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="16" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B70" s="23">
         <v>4.68</v>
@@ -24413,7 +24419,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -24461,7 +24467,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B72" s="15">
         <v>0.0</v>
@@ -24517,7 +24523,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -24565,7 +24571,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B74" s="21">
         <v>-11.7</v>
@@ -24597,7 +24603,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B75" s="15">
         <v>0.0</v>
@@ -24627,7 +24633,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -24671,7 +24677,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B77" s="22">
         <v>-148.62</v>
@@ -24731,7 +24737,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -24761,7 +24767,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -24791,7 +24797,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -24821,7 +24827,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -24851,7 +24857,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -24881,7 +24887,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -24933,7 +24939,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B84" s="21">
         <v>-52.66</v>
@@ -24971,7 +24977,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -25035,7 +25041,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B87" s="21">
         <v>-38.62</v>
@@ -25083,7 +25089,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B88" s="21">
         <v>-1.17</v>
@@ -25131,7 +25137,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B89" s="21">
         <v>-1.17</v>
@@ -25167,7 +25173,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="16" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B90" s="25">
         <v>-253.95</v>
@@ -25235,7 +25241,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B91" s="19">
         <v>452.89</v>
@@ -25287,7 +25293,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B92" s="19">
         <v>1340.89</v>
@@ -25355,7 +25361,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B93" s="15">
         <v>0.0</v>
@@ -25423,7 +25429,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B94" s="19">
         <v>1798.09</v>
@@ -25491,7 +25497,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -25521,7 +25527,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B96" s="18">
         <v>452.89</v>
@@ -25589,7 +25595,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -26548,7 +26554,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -27073,7 +27079,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -27170,2609 +27176,2609 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
+      <c r="A20" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>478</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="B21" s="30">
         <v>1448.68</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>1372.65</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>1879.95</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>2997.76</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>4481.19</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>4818.17</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>4660.82</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>4063.02</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>6050.31</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>7533.55</v>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="30">
         <v>7200.8</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="30">
         <v>5479.31</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="30">
         <v>4350.53</v>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="30">
         <v>2130.99</v>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="30">
         <v>1805.21</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="30">
         <v>3050.73</v>
       </c>
-      <c r="R21" s="29">
+      <c r="R21" s="30">
         <v>5466.91</v>
       </c>
-      <c r="S21" s="29">
+      <c r="S21" s="30">
         <v>1788.62</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T21" s="30">
         <v>2171.02</v>
       </c>
-      <c r="U21" s="29">
+      <c r="U21" s="30">
         <v>2785.79</v>
       </c>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="B22" s="30">
         <v>2695.69</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>3478.74</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>4105.27</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>4355.53</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>4817.11</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="30">
         <v>5841.23</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="30">
         <v>6057.92</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="30">
         <v>6361.89</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="30">
         <v>6541.63</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="30">
         <v>5444.52</v>
       </c>
-      <c r="L22" s="29">
+      <c r="L22" s="30">
         <v>4611.28</v>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="30">
         <v>3693.93</v>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="30">
         <v>3495.85</v>
       </c>
-      <c r="O22" s="29">
+      <c r="O22" s="30">
         <v>2581.84</v>
       </c>
-      <c r="P22" s="29">
+      <c r="P22" s="30">
         <v>2695.89</v>
       </c>
-      <c r="Q22" s="29">
+      <c r="Q22" s="30">
         <v>2877.84</v>
       </c>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
+      <c r="A23" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="B24" s="30">
         <v>2517.85</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>1905.69</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>2227.8</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>3369.95</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>3632.21</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>3665.79</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <v>3613.78</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="30">
         <v>3554.76</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>5112.07</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="30">
         <v>7072.28</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="30">
         <v>7484.0</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="30">
         <v>4739.93</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="30">
         <v>3235.72</v>
       </c>
-      <c r="O24" s="29">
+      <c r="O24" s="30">
         <v>2451.0</v>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="30">
         <v>2011.01</v>
       </c>
-      <c r="Q24" s="29">
+      <c r="Q24" s="30">
         <v>3503.98</v>
       </c>
-      <c r="R24" s="29">
+      <c r="R24" s="30">
         <v>5143.45</v>
       </c>
-      <c r="S24" s="29">
+      <c r="S24" s="30">
         <v>1670.18</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T24" s="30">
         <v>3133.56</v>
       </c>
-      <c r="U24" s="29">
+      <c r="U24" s="30">
         <v>3378.79</v>
       </c>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="B25" s="30">
         <v>2973.56</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>3283.64</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>3580.47</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>3690.82</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>3920.48</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <v>4974.22</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="30">
         <v>5518.07</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="30">
         <v>5867.1</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="30">
         <v>5887.71</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="30">
         <v>5093.67</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="30">
         <v>4388.94</v>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="30">
         <v>3536.47</v>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="30">
         <v>3421.98</v>
       </c>
-      <c r="O25" s="29">
+      <c r="O25" s="30">
         <v>2695.16</v>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="30">
         <v>2935.73</v>
       </c>
-      <c r="Q25" s="29">
+      <c r="Q25" s="30">
         <v>3190.13</v>
       </c>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>482</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>483</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="A27" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="B27" s="32">
         <v>13.59</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>10.47</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <v>12.17</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>18.24</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>20.07</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>19.93</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>19.93</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>19.62</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>27.57</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <v>39.14</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <v>41.47</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <v>29.59</v>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <v>20.06</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>15.2</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>12.17</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="32">
         <v>21.83</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="32">
         <v>32.07</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>11.09</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="32">
         <v>20.9</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="32">
         <v>22.48</v>
       </c>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>484</v>
-      </c>
-      <c r="B28" s="31">
+      <c r="A28" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="B28" s="32">
         <v>16.24</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>17.94</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>19.6</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>20.24</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>21.45</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>27.27</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <v>30.38</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="32">
         <v>33.06</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="32">
         <v>33.69</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <v>29.75</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="32">
         <v>26.19</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="32">
         <v>21.92</v>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="32">
         <v>21.21</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="32">
         <v>16.82</v>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="32">
         <v>18.6</v>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="32">
         <v>20.53</v>
       </c>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>485</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="27"/>
+      <c r="A29" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>486</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="A30" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="B30" s="33">
         <v>26.76</v>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="33">
         <v>22.24</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="33">
         <v>3.04</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="33">
         <v>21.99</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="33">
         <v>4.54</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="33">
         <v>9.04</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="33">
         <v>17.2</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="33">
         <v>22.82</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <v>-3.25</v>
       </c>
-      <c r="K30" s="32">
+      <c r="K30" s="33">
         <v>0.55</v>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="33">
         <v>8.58</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>-7.61</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="33">
         <v>0.62</v>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="33">
         <v>13.85</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="33">
         <v>0.4</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="33">
         <v>16.16</v>
       </c>
-      <c r="R30" s="32">
+      <c r="R30" s="33">
         <v>14.75</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="34">
         <v>-13.43</v>
       </c>
-      <c r="T30" s="32">
+      <c r="T30" s="33">
         <v>8.38</v>
       </c>
-      <c r="U30" s="32"/>
-      <c r="V30" s="32"/>
-      <c r="W30" s="32"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>487</v>
-      </c>
-      <c r="B31" s="32">
+      <c r="A31" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="B31" s="33">
         <v>14.73</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="33">
         <v>11.5</v>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="33">
         <v>11.72</v>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="33">
         <v>14.98</v>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="33">
         <v>9.07</v>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="33">
         <v>6.95</v>
       </c>
-      <c r="H31" s="32">
+      <c r="H31" s="33">
         <v>7.15</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="33">
         <v>3.03</v>
       </c>
-      <c r="J31" s="32">
+      <c r="J31" s="33">
         <v>0.41</v>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="33">
         <v>2.73</v>
       </c>
-      <c r="L31" s="32">
+      <c r="L31" s="33">
         <v>3.15</v>
       </c>
-      <c r="M31" s="32">
+      <c r="M31" s="33">
         <v>4.22</v>
       </c>
-      <c r="N31" s="32">
+      <c r="N31" s="33">
         <v>10.47</v>
       </c>
-      <c r="O31" s="32">
+      <c r="O31" s="33">
         <v>10.15</v>
       </c>
-      <c r="P31" s="32">
+      <c r="P31" s="33">
         <v>9.13</v>
       </c>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="32"/>
-      <c r="U31" s="32"/>
-      <c r="V31" s="32"/>
-      <c r="W31" s="32"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="33"/>
+      <c r="U31" s="33"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="26" t="s">
-        <v>488</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
+      <c r="A32" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="B33" s="32">
+      <c r="A33" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B33" s="33">
         <v>6.09</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="33">
         <v>7.87</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="33">
         <v>5.51</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="33">
         <v>2.3</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="33">
         <v>2.99</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <v>4.73</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="33">
         <v>4.44</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="33">
         <v>4.55</v>
       </c>
-      <c r="J33" s="32">
+      <c r="J33" s="33">
         <v>5.0</v>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="33">
         <v>3.02</v>
       </c>
-      <c r="L33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="N33" s="32">
+      <c r="L33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="33">
         <v>1.96</v>
       </c>
-      <c r="O33" s="32">
+      <c r="O33" s="33">
         <v>2.28</v>
       </c>
-      <c r="P33" s="32">
+      <c r="P33" s="33">
         <v>2.41</v>
       </c>
-      <c r="Q33" s="32">
+      <c r="Q33" s="33">
         <v>3.25</v>
       </c>
-      <c r="R33" s="32">
+      <c r="R33" s="33">
         <v>1.57</v>
       </c>
-      <c r="S33" s="32">
+      <c r="S33" s="33">
         <v>5.31</v>
       </c>
-      <c r="T33" s="32">
+      <c r="T33" s="33">
         <v>1.73</v>
       </c>
-      <c r="U33" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="V33" s="32"/>
-      <c r="W33" s="32"/>
+      <c r="U33" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="V33" s="33"/>
+      <c r="W33" s="33"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="B34" s="32">
+      <c r="A34" s="29" t="s">
+        <v>491</v>
+      </c>
+      <c r="B34" s="33">
         <v>4.36</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <v>4.2</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="33">
         <v>3.88</v>
       </c>
-      <c r="E34" s="32">
+      <c r="E34" s="33">
         <v>3.83</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="33">
         <v>4.39</v>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="33">
         <v>4.15</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="33">
         <v>2.92</v>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="33">
         <v>2.16</v>
       </c>
-      <c r="J34" s="32">
+      <c r="J34" s="33">
         <v>1.85</v>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="33">
         <v>1.37</v>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="33">
         <v>0.97</v>
       </c>
-      <c r="M34" s="32">
+      <c r="M34" s="33">
         <v>1.84</v>
       </c>
-      <c r="N34" s="32">
+      <c r="N34" s="33">
         <v>2.23</v>
       </c>
-      <c r="O34" s="32">
+      <c r="O34" s="33">
         <v>2.6</v>
       </c>
-      <c r="P34" s="32">
+      <c r="P34" s="33">
         <v>2.46</v>
       </c>
-      <c r="Q34" s="32">
+      <c r="Q34" s="33">
         <v>1.96</v>
       </c>
-      <c r="R34" s="32"/>
-      <c r="S34" s="32"/>
-      <c r="T34" s="32"/>
-      <c r="U34" s="32"/>
-      <c r="V34" s="32"/>
-      <c r="W34" s="32"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="33"/>
+      <c r="V34" s="33"/>
+      <c r="W34" s="33"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>491</v>
-      </c>
-      <c r="B35" s="32">
+      <c r="A35" s="29" t="s">
+        <v>492</v>
+      </c>
+      <c r="B35" s="33">
         <v>6.09</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="33">
         <v>7.87</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="33">
         <v>5.51</v>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="33">
         <v>2.3</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="33">
         <v>2.99</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="33">
         <v>4.73</v>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="33">
         <v>4.44</v>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="33">
         <v>4.55</v>
       </c>
-      <c r="J35" s="32">
+      <c r="J35" s="33">
         <v>5.0</v>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="33">
         <v>3.02</v>
       </c>
-      <c r="L35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="32">
+      <c r="L35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="33">
         <v>1.96</v>
       </c>
-      <c r="O35" s="32">
+      <c r="O35" s="33">
         <v>2.28</v>
       </c>
-      <c r="P35" s="32">
+      <c r="P35" s="33">
         <v>3.0</v>
       </c>
-      <c r="Q35" s="32">
+      <c r="Q35" s="33">
         <v>4.04</v>
       </c>
-      <c r="R35" s="32">
+      <c r="R35" s="33">
         <v>1.95</v>
       </c>
-      <c r="S35" s="32">
+      <c r="S35" s="33">
         <v>6.61</v>
       </c>
-      <c r="T35" s="32">
+      <c r="T35" s="33">
         <v>2.15</v>
       </c>
-      <c r="U35" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="V35" s="32"/>
-      <c r="W35" s="32"/>
+      <c r="U35" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>492</v>
-      </c>
-      <c r="B36" s="32">
+      <c r="A36" s="29" t="s">
+        <v>493</v>
+      </c>
+      <c r="B36" s="33">
         <v>4.36</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <v>4.2</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="33">
         <v>3.88</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="33">
         <v>3.83</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="33">
         <v>4.39</v>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="33">
         <v>4.15</v>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="33">
         <v>2.92</v>
       </c>
-      <c r="I36" s="32">
+      <c r="I36" s="33">
         <v>2.16</v>
       </c>
-      <c r="J36" s="32">
+      <c r="J36" s="33">
         <v>1.85</v>
       </c>
-      <c r="K36" s="32">
+      <c r="K36" s="33">
         <v>1.37</v>
       </c>
-      <c r="L36" s="32">
+      <c r="L36" s="33">
         <v>1.04</v>
       </c>
-      <c r="M36" s="32">
+      <c r="M36" s="33">
         <v>2.1</v>
       </c>
-      <c r="N36" s="32">
+      <c r="N36" s="33">
         <v>2.6</v>
       </c>
-      <c r="O36" s="32">
+      <c r="O36" s="33">
         <v>3.13</v>
       </c>
-      <c r="P36" s="32">
+      <c r="P36" s="33">
         <v>3.06</v>
       </c>
-      <c r="Q36" s="32">
+      <c r="Q36" s="33">
         <v>2.43</v>
       </c>
-      <c r="R36" s="32"/>
-      <c r="S36" s="32"/>
-      <c r="T36" s="32"/>
-      <c r="U36" s="32"/>
-      <c r="V36" s="32"/>
-      <c r="W36" s="32"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="33"/>
+      <c r="V36" s="33"/>
+      <c r="W36" s="33"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>493</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>494</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="29" t="s">
+        <v>495</v>
+      </c>
+      <c r="B38" s="32">
         <v>2.11</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>1.21</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>1.15</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>1.4</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>1.68</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>2.03</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>2.34</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>2.02</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>2.57</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>3.81</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="32">
         <v>4.03</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="32">
         <v>7.32</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="32">
         <v>1.39</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="32">
         <v>1.07</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="32">
         <v>0.84</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="32">
         <v>1.27</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="32">
         <v>2.43</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="32">
         <v>0.92</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="32">
         <v>2.02</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="32">
         <v>2.24</v>
       </c>
-      <c r="V38" s="30"/>
-      <c r="W38" s="30"/>
+      <c r="V38" s="31"/>
+      <c r="W38" s="31"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>495</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="B39" s="32">
         <v>1.47</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>1.51</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>1.69</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>1.85</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>2.11</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <v>2.6</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="32">
         <v>3.0</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="32">
         <v>3.53</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="32">
         <v>3.12</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="32">
         <v>2.59</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="32">
         <v>1.93</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="32">
         <v>1.48</v>
       </c>
-      <c r="N39" s="31">
+      <c r="N39" s="32">
         <v>1.36</v>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="32">
         <v>1.3</v>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="32">
         <v>1.47</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="32">
         <v>1.74</v>
       </c>
-      <c r="R39" s="30"/>
-      <c r="S39" s="30"/>
-      <c r="T39" s="30"/>
-      <c r="U39" s="30"/>
-      <c r="V39" s="30"/>
-      <c r="W39" s="30"/>
+      <c r="R39" s="31"/>
+      <c r="S39" s="31"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="31"/>
+      <c r="V39" s="31"/>
+      <c r="W39" s="31"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>496</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
+      <c r="A40" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="29" t="s">
+        <v>498</v>
+      </c>
+      <c r="B41" s="32">
         <v>3.71</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>1.84</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>1.64</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>2.19</v>
       </c>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="30"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="31">
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="32">
         <v>16.16</v>
       </c>
-      <c r="R41" s="31">
+      <c r="R41" s="32">
         <v>7.14</v>
       </c>
-      <c r="S41" s="31">
+      <c r="S41" s="32">
         <v>1.96</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="32">
         <v>2.29</v>
       </c>
-      <c r="U41" s="31">
+      <c r="U41" s="32">
         <v>2.77</v>
       </c>
-      <c r="V41" s="30"/>
-      <c r="W41" s="30"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="B42" s="32">
         <v>4.45</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>30.67</v>
       </c>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="31">
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="32">
         <v>10.8</v>
       </c>
-      <c r="P42" s="31">
+      <c r="P42" s="32">
         <v>5.16</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="32">
         <v>3.83</v>
       </c>
-      <c r="R42" s="30"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="30"/>
-      <c r="V42" s="30"/>
-      <c r="W42" s="30"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="31"/>
+      <c r="W42" s="31"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>499</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-      <c r="W43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>500</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="29" t="s">
+        <v>501</v>
+      </c>
+      <c r="B44" s="32">
         <v>0.11</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>0.1</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>0.13</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>0.21</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>0.25</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>0.19</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>0.21</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>0.23</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>0.33</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>0.49</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="32">
         <v>0.47</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="32">
         <v>0.33</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="32">
         <v>0.24</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="32">
         <v>0.13</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="32">
         <v>0.12</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="32">
         <v>0.23</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="32">
         <v>0.38</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="32">
         <v>0.11</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="32">
         <v>0.29</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="32">
         <v>0.31</v>
       </c>
-      <c r="V44" s="30"/>
-      <c r="W44" s="30"/>
+      <c r="V44" s="31"/>
+      <c r="W44" s="31"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>501</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="29" t="s">
+        <v>502</v>
+      </c>
+      <c r="B45" s="32">
         <v>0.16</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <v>0.17</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <v>0.2</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <v>0.22</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <v>0.24</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <v>0.29</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="32">
         <v>0.35</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="32">
         <v>0.37</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="32">
         <v>0.37</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="32">
         <v>0.31</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="32">
         <v>0.23</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="32">
         <v>0.2</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N45" s="32">
         <v>0.21</v>
       </c>
-      <c r="O45" s="31">
+      <c r="O45" s="32">
         <v>0.19</v>
       </c>
-      <c r="P45" s="31">
+      <c r="P45" s="32">
         <v>0.22</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="32">
         <v>0.26</v>
       </c>
-      <c r="R45" s="30"/>
-      <c r="S45" s="30"/>
-      <c r="T45" s="30"/>
-      <c r="U45" s="30"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="30"/>
+      <c r="R45" s="31"/>
+      <c r="S45" s="31"/>
+      <c r="T45" s="31"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="31"/>
+      <c r="W45" s="31"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
+      <c r="A46" s="27" t="s">
+        <v>503</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>503</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="29" t="s">
+        <v>504</v>
+      </c>
+      <c r="B47" s="32">
         <v>3.74</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <v>4.5</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <v>32.89</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <v>4.55</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <v>22.05</v>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="32">
         <v>11.06</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="32">
         <v>5.82</v>
       </c>
-      <c r="I47" s="31">
+      <c r="I47" s="32">
         <v>4.38</v>
       </c>
-      <c r="J47" s="30"/>
-      <c r="K47" s="29">
+      <c r="J47" s="31"/>
+      <c r="K47" s="30">
         <v>181.81</v>
       </c>
-      <c r="L47" s="31">
+      <c r="L47" s="32">
         <v>11.65</v>
       </c>
-      <c r="M47" s="30"/>
-      <c r="N47" s="29">
+      <c r="M47" s="31"/>
+      <c r="N47" s="30">
         <v>160.61</v>
       </c>
-      <c r="O47" s="31">
+      <c r="O47" s="32">
         <v>7.22</v>
       </c>
-      <c r="P47" s="29">
+      <c r="P47" s="30">
         <v>251.99</v>
       </c>
-      <c r="Q47" s="31">
+      <c r="Q47" s="32">
         <v>6.19</v>
       </c>
-      <c r="R47" s="31">
+      <c r="R47" s="32">
         <v>6.78</v>
       </c>
-      <c r="S47" s="30"/>
-      <c r="T47" s="31">
+      <c r="S47" s="31"/>
+      <c r="T47" s="32">
         <v>11.93</v>
       </c>
-      <c r="U47" s="30"/>
-      <c r="V47" s="30"/>
-      <c r="W47" s="30"/>
+      <c r="U47" s="31"/>
+      <c r="V47" s="31"/>
+      <c r="W47" s="31"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>504</v>
-      </c>
-      <c r="B48" s="31">
+      <c r="A48" s="29" t="s">
+        <v>505</v>
+      </c>
+      <c r="B48" s="32">
         <v>6.79</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <v>8.7</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="32">
         <v>8.53</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="32">
         <v>6.68</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="32">
         <v>11.02</v>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="32">
         <v>14.39</v>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="32">
         <v>13.99</v>
       </c>
-      <c r="I48" s="31">
+      <c r="I48" s="32">
         <v>32.95</v>
       </c>
-      <c r="J48" s="29">
+      <c r="J48" s="30">
         <v>246.53</v>
       </c>
-      <c r="K48" s="31">
+      <c r="K48" s="32">
         <v>36.62</v>
       </c>
-      <c r="L48" s="31">
+      <c r="L48" s="32">
         <v>31.74</v>
       </c>
-      <c r="M48" s="31">
+      <c r="M48" s="32">
         <v>23.68</v>
       </c>
-      <c r="N48" s="31">
+      <c r="N48" s="32">
         <v>9.55</v>
       </c>
-      <c r="O48" s="31">
+      <c r="O48" s="32">
         <v>9.85</v>
       </c>
-      <c r="P48" s="31">
+      <c r="P48" s="32">
         <v>10.96</v>
       </c>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="30"/>
-      <c r="S48" s="30"/>
-      <c r="T48" s="30"/>
-      <c r="U48" s="30"/>
-      <c r="V48" s="30"/>
-      <c r="W48" s="30"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
+      <c r="S48" s="31"/>
+      <c r="T48" s="31"/>
+      <c r="U48" s="31"/>
+      <c r="V48" s="31"/>
+      <c r="W48" s="31"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
-        <v>505</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
+      <c r="A49" s="27" t="s">
+        <v>506</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="31">
+      <c r="A50" s="29" t="s">
+        <v>507</v>
+      </c>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="32">
         <v>15.62</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>15.28</v>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <v>6.59</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="32">
         <v>7.38</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="32">
         <v>10.3</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="32">
         <v>9.83</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="32">
         <v>10.56</v>
       </c>
-      <c r="L50" s="31">
+      <c r="L50" s="32">
         <v>11.43</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="32">
         <v>7.21</v>
       </c>
-      <c r="N50" s="31">
+      <c r="N50" s="32">
         <v>9.01</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="32">
         <v>9.43</v>
       </c>
-      <c r="P50" s="30"/>
-      <c r="Q50" s="31">
+      <c r="P50" s="31"/>
+      <c r="Q50" s="32">
         <v>29.55</v>
       </c>
-      <c r="R50" s="31">
+      <c r="R50" s="32">
         <v>16.69</v>
       </c>
-      <c r="S50" s="31">
+      <c r="S50" s="32">
         <v>5.75</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="32">
         <v>22.82</v>
       </c>
-      <c r="U50" s="30"/>
-      <c r="V50" s="30"/>
-      <c r="W50" s="30"/>
+      <c r="U50" s="31"/>
+      <c r="V50" s="31"/>
+      <c r="W50" s="31"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="B51" s="31">
+      <c r="A51" s="29" t="s">
+        <v>508</v>
+      </c>
+      <c r="B51" s="32">
         <v>89.47</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <v>17.0</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="32">
         <v>11.39</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="32">
         <v>9.67</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="32">
         <v>9.14</v>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <v>8.99</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="32">
         <v>10.04</v>
       </c>
-      <c r="I51" s="31">
+      <c r="I51" s="32">
         <v>9.72</v>
       </c>
-      <c r="J51" s="31">
+      <c r="J51" s="32">
         <v>9.55</v>
       </c>
-      <c r="K51" s="31">
+      <c r="K51" s="32">
         <v>9.49</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="32">
         <v>10.75</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="32">
         <v>12.31</v>
       </c>
-      <c r="N51" s="31">
+      <c r="N51" s="32">
         <v>16.67</v>
       </c>
-      <c r="O51" s="31">
+      <c r="O51" s="32">
         <v>16.49</v>
       </c>
-      <c r="P51" s="31">
+      <c r="P51" s="32">
         <v>20.34</v>
       </c>
-      <c r="Q51" s="30"/>
-      <c r="R51" s="30"/>
-      <c r="S51" s="30"/>
-      <c r="T51" s="30"/>
-      <c r="U51" s="30"/>
-      <c r="V51" s="30"/>
-      <c r="W51" s="30"/>
+      <c r="Q51" s="31"/>
+      <c r="R51" s="31"/>
+      <c r="S51" s="31"/>
+      <c r="T51" s="31"/>
+      <c r="U51" s="31"/>
+      <c r="V51" s="31"/>
+      <c r="W51" s="31"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>508</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>509</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="31">
+      <c r="A53" s="29" t="s">
+        <v>510</v>
+      </c>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="32">
         <v>65.73</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="32">
         <v>40.1</v>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="32">
         <v>30.54</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="32">
         <v>45.94</v>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="32">
         <v>33.27</v>
       </c>
-      <c r="J53" s="31">
+      <c r="J53" s="32">
         <v>19.31</v>
       </c>
-      <c r="K53" s="31">
+      <c r="K53" s="32">
         <v>18.7</v>
       </c>
-      <c r="L53" s="31">
+      <c r="L53" s="32">
         <v>17.23</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="32">
         <v>11.28</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="32">
         <v>22.54</v>
       </c>
-      <c r="O53" s="31">
+      <c r="O53" s="32">
         <v>20.25</v>
       </c>
-      <c r="P53" s="30"/>
-      <c r="Q53" s="29">
+      <c r="P53" s="31"/>
+      <c r="Q53" s="30">
         <v>121.4</v>
       </c>
-      <c r="R53" s="31">
+      <c r="R53" s="32">
         <v>14.74</v>
       </c>
-      <c r="S53" s="31">
+      <c r="S53" s="32">
         <v>6.25</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="32">
         <v>16.94</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="32">
         <v>29.23</v>
       </c>
-      <c r="V53" s="30"/>
-      <c r="W53" s="30"/>
+      <c r="V53" s="31"/>
+      <c r="W53" s="31"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>510</v>
-      </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="29">
+      <c r="A54" s="29" t="s">
+        <v>511</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="30">
         <v>127.51</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="32">
         <v>39.83</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="32">
         <v>29.69</v>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="32">
         <v>24.05</v>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="32">
         <v>21.15</v>
       </c>
-      <c r="I54" s="31">
+      <c r="I54" s="32">
         <v>17.1</v>
       </c>
-      <c r="J54" s="31">
+      <c r="J54" s="32">
         <v>16.72</v>
       </c>
-      <c r="K54" s="31">
+      <c r="K54" s="32">
         <v>16.71</v>
       </c>
-      <c r="L54" s="31">
+      <c r="L54" s="32">
         <v>22.75</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="32">
         <v>32.6</v>
       </c>
-      <c r="N54" s="31">
+      <c r="N54" s="32">
         <v>36.96</v>
       </c>
-      <c r="O54" s="31">
+      <c r="O54" s="32">
         <v>27.26</v>
       </c>
-      <c r="P54" s="31">
+      <c r="P54" s="32">
         <v>25.39</v>
       </c>
-      <c r="Q54" s="31">
+      <c r="Q54" s="32">
         <v>18.37</v>
       </c>
-      <c r="R54" s="30"/>
-      <c r="S54" s="30"/>
-      <c r="T54" s="30"/>
-      <c r="U54" s="30"/>
-      <c r="V54" s="30"/>
-      <c r="W54" s="30"/>
+      <c r="R54" s="31"/>
+      <c r="S54" s="31"/>
+      <c r="T54" s="31"/>
+      <c r="U54" s="31"/>
+      <c r="V54" s="31"/>
+      <c r="W54" s="31"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="26" t="s">
-        <v>511</v>
-      </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="27"/>
-      <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-      <c r="U55" s="27"/>
-      <c r="V55" s="27"/>
-      <c r="W55" s="27"/>
+      <c r="A55" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="28"/>
+      <c r="Q55" s="28"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="28"/>
+      <c r="T55" s="28"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="28"/>
+      <c r="W55" s="28"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="29">
+      <c r="A56" s="29" t="s">
+        <v>513</v>
+      </c>
+      <c r="B56" s="31"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="30">
         <v>164.35</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>21.04</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <v>26.36</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <v>27.61</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="32">
         <v>27.84</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="32">
         <v>11.7</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="32">
         <v>17.22</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="32">
         <v>17.77</v>
       </c>
-      <c r="L56" s="31">
+      <c r="L56" s="32">
         <v>17.47</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="32">
         <v>10.79</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="32">
         <v>15.3</v>
       </c>
-      <c r="O56" s="31">
+      <c r="O56" s="32">
         <v>19.08</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="32">
         <v>28.0</v>
       </c>
-      <c r="Q56" s="29">
+      <c r="Q56" s="30">
         <v>121.4</v>
       </c>
-      <c r="R56" s="31">
+      <c r="R56" s="32">
         <v>21.76</v>
       </c>
-      <c r="S56" s="31">
+      <c r="S56" s="32">
         <v>8.52</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>54.08</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="32">
         <v>45.47</v>
       </c>
-      <c r="V56" s="30"/>
-      <c r="W56" s="30"/>
+      <c r="V56" s="31"/>
+      <c r="W56" s="31"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>513</v>
-      </c>
-      <c r="B57" s="31">
+      <c r="A57" s="29" t="s">
+        <v>514</v>
+      </c>
+      <c r="B57" s="32">
         <v>1.47</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <v>1.51</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="32">
         <v>1.69</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="32">
         <v>1.85</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="32">
         <v>2.11</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="32">
         <v>2.6</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="32">
         <v>3.0</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="32">
         <v>3.53</v>
       </c>
-      <c r="J57" s="31">
+      <c r="J57" s="32">
         <v>3.12</v>
       </c>
-      <c r="K57" s="31">
+      <c r="K57" s="32">
         <v>2.59</v>
       </c>
-      <c r="L57" s="31">
+      <c r="L57" s="32">
         <v>1.93</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="32">
         <v>1.48</v>
       </c>
-      <c r="N57" s="31">
+      <c r="N57" s="32">
         <v>1.36</v>
       </c>
-      <c r="O57" s="31">
+      <c r="O57" s="32">
         <v>1.3</v>
       </c>
-      <c r="P57" s="31">
+      <c r="P57" s="32">
         <v>1.47</v>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="32">
         <v>1.74</v>
       </c>
-      <c r="R57" s="30"/>
-      <c r="S57" s="30"/>
-      <c r="T57" s="30"/>
-      <c r="U57" s="30"/>
-      <c r="V57" s="30"/>
-      <c r="W57" s="30"/>
+      <c r="R57" s="31"/>
+      <c r="S57" s="31"/>
+      <c r="T57" s="31"/>
+      <c r="U57" s="31"/>
+      <c r="V57" s="31"/>
+      <c r="W57" s="31"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="26" t="s">
-        <v>514</v>
-      </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
+      <c r="A58" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="Q58" s="28"/>
+      <c r="R58" s="28"/>
+      <c r="S58" s="28"/>
+      <c r="T58" s="28"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="28"/>
+      <c r="W58" s="28"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>515</v>
-      </c>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="34">
+      <c r="A59" s="29" t="s">
+        <v>516</v>
+      </c>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="35">
         <v>-1.4</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <v>-2.04</v>
       </c>
-      <c r="G59" s="31">
+      <c r="G59" s="32">
         <v>0.74</v>
       </c>
-      <c r="H59" s="34">
+      <c r="H59" s="35">
         <v>-1.77</v>
       </c>
-      <c r="I59" s="34">
+      <c r="I59" s="35">
         <v>-0.56</v>
       </c>
-      <c r="J59" s="34">
+      <c r="J59" s="35">
         <v>-0.52</v>
       </c>
-      <c r="K59" s="34">
+      <c r="K59" s="35">
         <v>-2.31</v>
       </c>
-      <c r="L59" s="34">
+      <c r="L59" s="35">
         <v>-1.27</v>
       </c>
-      <c r="M59" s="31">
+      <c r="M59" s="32">
         <v>0.07</v>
       </c>
-      <c r="N59" s="31">
+      <c r="N59" s="32">
         <v>5.2</v>
       </c>
-      <c r="O59" s="31">
+      <c r="O59" s="32">
         <v>0.12</v>
       </c>
-      <c r="P59" s="30"/>
-      <c r="Q59" s="34">
+      <c r="P59" s="31"/>
+      <c r="Q59" s="35">
         <v>-1.33</v>
       </c>
-      <c r="R59" s="31">
+      <c r="R59" s="32">
         <v>0.34</v>
       </c>
-      <c r="S59" s="31">
+      <c r="S59" s="32">
         <v>0.36</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="32">
         <v>0.26</v>
       </c>
-      <c r="U59" s="34">
+      <c r="U59" s="35">
         <v>-1.66</v>
       </c>
-      <c r="V59" s="30"/>
-      <c r="W59" s="30"/>
+      <c r="V59" s="31"/>
+      <c r="W59" s="31"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="34">
+      <c r="A60" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="35">
         <v>-1.38</v>
       </c>
-      <c r="F60" s="34">
+      <c r="F60" s="35">
         <v>-1.13</v>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="35">
         <v>-0.99</v>
       </c>
-      <c r="H60" s="34">
+      <c r="H60" s="35">
         <v>-0.67</v>
       </c>
-      <c r="I60" s="34">
+      <c r="I60" s="35">
         <v>-1.55</v>
       </c>
-      <c r="J60" s="31">
+      <c r="J60" s="32">
         <v>2.31</v>
       </c>
-      <c r="K60" s="30"/>
-      <c r="L60" s="31">
+      <c r="K60" s="31"/>
+      <c r="L60" s="32">
         <v>0.37</v>
       </c>
-      <c r="M60" s="31">
+      <c r="M60" s="32">
         <v>16.0</v>
       </c>
-      <c r="N60" s="34">
+      <c r="N60" s="35">
         <v>-3.62</v>
       </c>
-      <c r="O60" s="34">
+      <c r="O60" s="35">
         <v>-3.39</v>
       </c>
-      <c r="P60" s="30"/>
-      <c r="Q60" s="34">
+      <c r="P60" s="31"/>
+      <c r="Q60" s="35">
         <v>-0.67</v>
       </c>
-      <c r="R60" s="30"/>
-      <c r="S60" s="30"/>
-      <c r="T60" s="30"/>
-      <c r="U60" s="30"/>
-      <c r="V60" s="30"/>
-      <c r="W60" s="30"/>
+      <c r="R60" s="31"/>
+      <c r="S60" s="31"/>
+      <c r="T60" s="31"/>
+      <c r="U60" s="31"/>
+      <c r="V60" s="31"/>
+      <c r="W60" s="31"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="26" t="s">
-        <v>517</v>
-      </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27"/>
+      <c r="A61" s="27" t="s">
+        <v>518</v>
+      </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+      <c r="P61" s="28"/>
+      <c r="Q61" s="28"/>
+      <c r="R61" s="28"/>
+      <c r="S61" s="28"/>
+      <c r="T61" s="28"/>
+      <c r="U61" s="28"/>
+      <c r="V61" s="28"/>
+      <c r="W61" s="28"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="29" t="s">
+        <v>519</v>
+      </c>
+      <c r="B62" s="32">
         <v>0.06</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>0.07</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>0.11</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>0.19</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>0.31</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>0.26</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>0.28</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>0.26</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>0.4</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="32">
         <v>0.52</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="32">
         <v>0.46</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="32">
         <v>0.38</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="32">
         <v>0.32</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="32">
         <v>0.12</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="32">
         <v>0.11</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="32">
         <v>0.2</v>
       </c>
-      <c r="R62" s="31">
+      <c r="R62" s="32">
         <v>0.42</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="32">
         <v>0.12</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="32">
         <v>0.2</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="32">
         <v>0.25</v>
       </c>
-      <c r="V62" s="30"/>
-      <c r="W62" s="30"/>
+      <c r="V62" s="31"/>
+      <c r="W62" s="31"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>519</v>
-      </c>
-      <c r="B63" s="31">
+      <c r="A63" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="B63" s="32">
         <v>0.14</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <v>0.19</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="32">
         <v>0.23</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="32">
         <v>0.26</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="32">
         <v>0.3</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="32">
         <v>0.34</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="32">
         <v>0.38</v>
       </c>
-      <c r="I63" s="31">
+      <c r="I63" s="32">
         <v>0.41</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="32">
         <v>0.42</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="32">
         <v>0.34</v>
       </c>
-      <c r="L63" s="31">
+      <c r="L63" s="32">
         <v>0.25</v>
       </c>
-      <c r="M63" s="31">
+      <c r="M63" s="32">
         <v>0.21</v>
       </c>
-      <c r="N63" s="31">
+      <c r="N63" s="32">
         <v>0.22</v>
       </c>
-      <c r="O63" s="31">
+      <c r="O63" s="32">
         <v>0.18</v>
       </c>
-      <c r="P63" s="31">
+      <c r="P63" s="32">
         <v>0.2</v>
       </c>
-      <c r="Q63" s="31">
+      <c r="Q63" s="32">
         <v>0.24</v>
       </c>
-      <c r="R63" s="30"/>
-      <c r="S63" s="30"/>
-      <c r="T63" s="30"/>
-      <c r="U63" s="30"/>
-      <c r="V63" s="30"/>
-      <c r="W63" s="30"/>
+      <c r="R63" s="31"/>
+      <c r="S63" s="31"/>
+      <c r="T63" s="31"/>
+      <c r="U63" s="31"/>
+      <c r="V63" s="31"/>
+      <c r="W63" s="31"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
+      <c r="A64" s="27" t="s">
+        <v>521</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="28"/>
+      <c r="R64" s="28"/>
+      <c r="S64" s="28"/>
+      <c r="T64" s="28"/>
+      <c r="U64" s="28"/>
+      <c r="V64" s="28"/>
+      <c r="W64" s="28"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>521</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="29" t="s">
+        <v>522</v>
+      </c>
+      <c r="B65" s="32">
         <v>3.52</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>3.48</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>5.51</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>8.24</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>14.63</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <v>7.36</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="32">
         <v>7.63</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>6.05</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>9.16</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="32">
         <v>9.02</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="32">
         <v>8.92</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="32">
         <v>7.37</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="32">
         <v>8.27</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="32">
         <v>6.19</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="32">
         <v>8.27</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="32">
         <v>18.39</v>
       </c>
-      <c r="R65" s="31">
+      <c r="R65" s="32">
         <v>12.65</v>
       </c>
-      <c r="S65" s="31">
+      <c r="S65" s="32">
         <v>4.06</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="32">
         <v>7.17</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="32">
         <v>18.82</v>
       </c>
-      <c r="V65" s="30"/>
-      <c r="W65" s="30"/>
+      <c r="V65" s="31"/>
+      <c r="W65" s="31"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>522</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="29" t="s">
+        <v>523</v>
+      </c>
+      <c r="B66" s="32">
         <v>6.95</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <v>7.71</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="32">
         <v>8.33</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="32">
         <v>8.06</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="32">
         <v>8.29</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="32">
         <v>7.93</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="32">
         <v>8.25</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="32">
         <v>8.17</v>
       </c>
-      <c r="J66" s="31">
+      <c r="J66" s="32">
         <v>8.55</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="32">
         <v>8.14</v>
       </c>
-      <c r="L66" s="31">
+      <c r="L66" s="32">
         <v>7.89</v>
       </c>
-      <c r="M66" s="31">
+      <c r="M66" s="32">
         <v>8.45</v>
       </c>
-      <c r="N66" s="31">
+      <c r="N66" s="32">
         <v>9.91</v>
       </c>
-      <c r="O66" s="31">
+      <c r="O66" s="32">
         <v>9.07</v>
       </c>
-      <c r="P66" s="31">
+      <c r="P66" s="32">
         <v>9.41</v>
       </c>
-      <c r="Q66" s="31">
+      <c r="Q66" s="32">
         <v>10.56</v>
       </c>
-      <c r="R66" s="30"/>
-      <c r="S66" s="30"/>
-      <c r="T66" s="30"/>
-      <c r="U66" s="30"/>
-      <c r="V66" s="30"/>
-      <c r="W66" s="30"/>
+      <c r="R66" s="31"/>
+      <c r="S66" s="31"/>
+      <c r="T66" s="31"/>
+      <c r="U66" s="31"/>
+      <c r="V66" s="31"/>
+      <c r="W66" s="31"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="26" t="s">
-        <v>523</v>
-      </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-      <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-      <c r="U67" s="27"/>
-      <c r="V67" s="27"/>
-      <c r="W67" s="27"/>
+      <c r="A67" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+      <c r="Q67" s="28"/>
+      <c r="R67" s="28"/>
+      <c r="S67" s="28"/>
+      <c r="T67" s="28"/>
+      <c r="U67" s="28"/>
+      <c r="V67" s="28"/>
+      <c r="W67" s="28"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
-        <v>524</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="29" t="s">
+        <v>525</v>
+      </c>
+      <c r="B68" s="32">
         <v>2.04</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>3.01</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>17.51</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>3.67</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>11.22</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <v>7.89</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="32">
         <v>5.61</v>
       </c>
-      <c r="I68" s="31">
+      <c r="I68" s="32">
         <v>3.99</v>
       </c>
-      <c r="J68" s="31">
+      <c r="J68" s="32">
         <v>25.93</v>
       </c>
-      <c r="K68" s="31">
+      <c r="K68" s="32">
         <v>20.69</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="32">
         <v>8.76</v>
       </c>
-      <c r="M68" s="30"/>
-      <c r="N68" s="31">
+      <c r="M68" s="31"/>
+      <c r="N68" s="32">
         <v>17.51</v>
       </c>
-      <c r="O68" s="31">
+      <c r="O68" s="32">
         <v>6.31</v>
       </c>
-      <c r="P68" s="31">
+      <c r="P68" s="32">
         <v>8.3</v>
       </c>
-      <c r="Q68" s="31">
+      <c r="Q68" s="32">
         <v>4.42</v>
       </c>
-      <c r="R68" s="31">
+      <c r="R68" s="32">
         <v>6.53</v>
       </c>
-      <c r="S68" s="30"/>
-      <c r="T68" s="31">
+      <c r="S68" s="31"/>
+      <c r="T68" s="32">
         <v>7.02</v>
       </c>
-      <c r="U68" s="30"/>
-      <c r="V68" s="30"/>
-      <c r="W68" s="30"/>
+      <c r="U68" s="31"/>
+      <c r="V68" s="31"/>
+      <c r="W68" s="31"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>525</v>
-      </c>
-      <c r="B69" s="31">
+      <c r="A69" s="29" t="s">
+        <v>526</v>
+      </c>
+      <c r="B69" s="32">
         <v>5.05</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <v>6.59</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="32">
         <v>6.79</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="32">
         <v>5.72</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="32">
         <v>7.78</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="32">
         <v>9.01</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="32">
         <v>9.14</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="32">
         <v>13.3</v>
       </c>
-      <c r="J69" s="31">
+      <c r="J69" s="32">
         <v>19.73</v>
       </c>
-      <c r="K69" s="31">
+      <c r="K69" s="32">
         <v>15.72</v>
       </c>
-      <c r="L69" s="31">
+      <c r="L69" s="32">
         <v>13.44</v>
       </c>
-      <c r="M69" s="31">
+      <c r="M69" s="32">
         <v>11.24</v>
       </c>
-      <c r="N69" s="31">
+      <c r="N69" s="32">
         <v>7.14</v>
       </c>
-      <c r="O69" s="31">
+      <c r="O69" s="32">
         <v>7.16</v>
       </c>
-      <c r="P69" s="31">
+      <c r="P69" s="32">
         <v>7.3</v>
       </c>
-      <c r="Q69" s="30"/>
-      <c r="R69" s="30"/>
-      <c r="S69" s="30"/>
-      <c r="T69" s="30"/>
-      <c r="U69" s="30"/>
-      <c r="V69" s="30"/>
-      <c r="W69" s="30"/>
+      <c r="Q69" s="31"/>
+      <c r="R69" s="31"/>
+      <c r="S69" s="31"/>
+      <c r="T69" s="31"/>
+      <c r="U69" s="31"/>
+      <c r="V69" s="31"/>
+      <c r="W69" s="31"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="26" t="s">
-        <v>526</v>
-      </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="27"/>
-      <c r="V70" s="27"/>
-      <c r="W70" s="27"/>
+      <c r="A70" s="27" t="s">
+        <v>527</v>
+      </c>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
+      <c r="N70" s="28"/>
+      <c r="O70" s="28"/>
+      <c r="P70" s="28"/>
+      <c r="Q70" s="28"/>
+      <c r="R70" s="28"/>
+      <c r="S70" s="28"/>
+      <c r="T70" s="28"/>
+      <c r="U70" s="28"/>
+      <c r="V70" s="28"/>
+      <c r="W70" s="28"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="28" t="s">
-        <v>527</v>
-      </c>
-      <c r="B71" s="31">
+      <c r="A71" s="29" t="s">
+        <v>528</v>
+      </c>
+      <c r="B71" s="32">
         <v>2.16</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="32">
         <v>3.25</v>
       </c>
-      <c r="D71" s="31">
+      <c r="D71" s="32">
         <v>28.01</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="32">
         <v>4.12</v>
       </c>
-      <c r="F71" s="31">
+      <c r="F71" s="32">
         <v>27.13</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="32">
         <v>14.74</v>
       </c>
-      <c r="H71" s="31">
+      <c r="H71" s="32">
         <v>7.49</v>
       </c>
-      <c r="I71" s="31">
+      <c r="I71" s="32">
         <v>5.0</v>
       </c>
-      <c r="J71" s="30"/>
-      <c r="K71" s="29">
+      <c r="J71" s="31"/>
+      <c r="K71" s="30">
         <v>192.95</v>
       </c>
-      <c r="L71" s="31">
+      <c r="L71" s="32">
         <v>11.4</v>
       </c>
-      <c r="M71" s="30"/>
-      <c r="N71" s="29">
+      <c r="M71" s="31"/>
+      <c r="N71" s="30">
         <v>217.4</v>
       </c>
-      <c r="O71" s="31">
+      <c r="O71" s="32">
         <v>6.31</v>
       </c>
-      <c r="P71" s="29">
+      <c r="P71" s="30">
         <v>233.33</v>
       </c>
-      <c r="Q71" s="31">
+      <c r="Q71" s="32">
         <v>5.4</v>
       </c>
-      <c r="R71" s="31">
+      <c r="R71" s="32">
         <v>7.41</v>
       </c>
-      <c r="S71" s="30"/>
-      <c r="T71" s="31">
+      <c r="S71" s="31"/>
+      <c r="T71" s="32">
         <v>8.27</v>
       </c>
-      <c r="U71" s="30"/>
-      <c r="V71" s="30"/>
-      <c r="W71" s="30"/>
+      <c r="U71" s="31"/>
+      <c r="V71" s="31"/>
+      <c r="W71" s="31"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="28" t="s">
-        <v>528</v>
-      </c>
-      <c r="B72" s="31">
+      <c r="A72" s="29" t="s">
+        <v>529</v>
+      </c>
+      <c r="B72" s="32">
         <v>6.18</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="32">
         <v>9.3</v>
       </c>
-      <c r="D72" s="31">
+      <c r="D72" s="32">
         <v>9.85</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="32">
         <v>7.92</v>
       </c>
-      <c r="F72" s="31">
+      <c r="F72" s="32">
         <v>13.64</v>
       </c>
-      <c r="G72" s="31">
+      <c r="G72" s="32">
         <v>16.98</v>
       </c>
-      <c r="H72" s="31">
+      <c r="H72" s="32">
         <v>15.48</v>
       </c>
-      <c r="I72" s="31">
+      <c r="I72" s="32">
         <v>33.55</v>
       </c>
-      <c r="J72" s="29">
+      <c r="J72" s="30">
         <v>206.35</v>
       </c>
-      <c r="K72" s="31">
+      <c r="K72" s="32">
         <v>38.14</v>
       </c>
-      <c r="L72" s="31">
+      <c r="L72" s="32">
         <v>31.9</v>
       </c>
-      <c r="M72" s="31">
+      <c r="M72" s="32">
         <v>24.89</v>
       </c>
-      <c r="N72" s="31">
+      <c r="N72" s="32">
         <v>9.94</v>
       </c>
-      <c r="O72" s="31">
+      <c r="O72" s="32">
         <v>9.48</v>
       </c>
-      <c r="P72" s="31">
+      <c r="P72" s="32">
         <v>10.09</v>
       </c>
-      <c r="Q72" s="30"/>
-      <c r="R72" s="30"/>
-      <c r="S72" s="30"/>
-      <c r="T72" s="30"/>
-      <c r="U72" s="30"/>
-      <c r="V72" s="30"/>
-      <c r="W72" s="30"/>
+      <c r="Q72" s="31"/>
+      <c r="R72" s="31"/>
+      <c r="S72" s="31"/>
+      <c r="T72" s="31"/>
+      <c r="U72" s="31"/>
+      <c r="V72" s="31"/>
+      <c r="W72" s="31"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
